--- a/server/master-excel-files/General_CHEMISTRY_Grade 6.xlsx
+++ b/server/master-excel-files/General_CHEMISTRY_Grade 6.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\CHEMISTRY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\CHEMISTRY\SUMERU\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -228,6 +228,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -245,9 +248,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -568,52 +568,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -623,7 +623,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -658,7 +658,7 @@
       <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -691,7 +691,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -726,7 +726,7 @@
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -759,7 +759,7 @@
       <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E7" s="1" t="s">

--- a/server/master-excel-files/General_CHEMISTRY_Grade 6.xlsx
+++ b/server/master-excel-files/General_CHEMISTRY_Grade 6.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\CHEMISTRY\SUMERU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\teacher-year-plan-app\server\master-excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -798,9 +798,12 @@
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="H8:I42 E1:K1 E3:K7">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 H8:I40">
       <formula1>"Not Started,In Progress,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E3:K7">
+      <formula1>"Not Assigned,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
